--- a/poker/resources/sample/poker/Blackjack.xlsx
+++ b/poker/resources/sample/poker/Blackjack.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\project2\poker\resources\sample\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\project2\poker\resources\sample\poker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80448956-1291-48E4-BDB9-1DFDDAC7D9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9800CF-CB6A-485E-9037-3B442A7A9FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="195" windowWidth="21225" windowHeight="11040" tabRatio="824" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9795" yWindow="2310" windowWidth="15330" windowHeight="11040" tabRatio="824" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blackjack" sheetId="34" r:id="rId1"/>
@@ -192,18 +192,21 @@
     <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -625,7 +628,7 @@
   <dimension ref="A1:O7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="2"/>
+    <col min="1" max="1" width="9.625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
     <col min="3" max="3" width="15.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="9" style="2"/>
@@ -772,7 +775,8 @@
     <row r="4" spans="1:15" s="1" customFormat="1"/>
     <row r="5" spans="1:15">
       <c r="A5" s="2">
-        <v>1</v>
+        <f>B5*10+D5</f>
+        <v>3001001</v>
       </c>
       <c r="B5" s="1">
         <v>300100</v>
@@ -819,7 +823,8 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="2">
-        <v>2</v>
+        <f t="shared" ref="A6:A7" si="0">B6*10+D6</f>
+        <v>3001002</v>
       </c>
       <c r="B6" s="1">
         <v>300100</v>
@@ -866,7 +871,8 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="2">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>3001003</v>
       </c>
       <c r="B7" s="1">
         <v>300100</v>
